--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,444 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129374419</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 47774, Lörstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>572731</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6406445</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129374400</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92872</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 47774, Lörstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>572739</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6406392</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129374458</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 47774, Lörstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>572658</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6406532</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129374446</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 47774, Lörstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>572696</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6406574</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129332504</v>
       </c>
       <c r="B2" t="n">
-        <v>91962</v>
+        <v>91971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129374400</v>
       </c>
       <c r="B4" t="n">
-        <v>92872</v>
+        <v>92857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1225,6 +1225,216 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129380036</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91992</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A47774 Lörstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>572732</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6406447</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129380034</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90572</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A47774 Lörstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>572732</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6406447</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129332504</v>
       </c>
       <c r="B2" t="n">
-        <v>91971</v>
+        <v>91972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -901,7 +901,7 @@
         <v>129374400</v>
       </c>
       <c r="B4" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1230,7 +1230,7 @@
         <v>129380036</v>
       </c>
       <c r="B7" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129332504</v>
       </c>
       <c r="B2" t="n">
-        <v>91972</v>
+        <v>91975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129374400</v>
       </c>
       <c r="B4" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>129380036</v>
       </c>
       <c r="B7" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>129380034</v>
       </c>
       <c r="B8" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129332504</v>
       </c>
       <c r="B2" t="n">
-        <v>91975</v>
+        <v>91977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129374400</v>
       </c>
       <c r="B4" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>129380036</v>
       </c>
       <c r="B7" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>129380034</v>
       </c>
       <c r="B8" t="n">
-        <v>90575</v>
+        <v>90577</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129332504</v>
       </c>
       <c r="B2" t="n">
-        <v>91977</v>
+        <v>91981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129374400</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>129380036</v>
       </c>
       <c r="B7" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>129380034</v>
       </c>
       <c r="B8" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129332504</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>91982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -901,7 +901,7 @@
         <v>129374400</v>
       </c>
       <c r="B4" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1230,7 +1230,7 @@
         <v>129380036</v>
       </c>
       <c r="B7" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>129380034</v>
       </c>
       <c r="B8" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129332504</v>
       </c>
       <c r="B2" t="n">
-        <v>91982</v>
+        <v>91985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129374400</v>
       </c>
       <c r="B4" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>129380036</v>
       </c>
       <c r="B7" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>129380034</v>
       </c>
       <c r="B8" t="n">
-        <v>90582</v>
+        <v>90585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129332504</v>
       </c>
       <c r="B2" t="n">
-        <v>91985</v>
+        <v>92013</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129374419</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129374400</v>
       </c>
       <c r="B4" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129374458</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129374446</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>129380036</v>
       </c>
       <c r="B7" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>129380034</v>
       </c>
       <c r="B8" t="n">
-        <v>90585</v>
+        <v>90613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129332504</v>
       </c>
       <c r="B2" t="n">
-        <v>92013</v>
+        <v>92019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129374419</v>
       </c>
       <c r="B3" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129374400</v>
       </c>
       <c r="B4" t="n">
-        <v>92899</v>
+        <v>92905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129374458</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129374446</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>129380036</v>
       </c>
       <c r="B7" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>129380034</v>
       </c>
       <c r="B8" t="n">
-        <v>90613</v>
+        <v>90619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129332504</v>
       </c>
       <c r="B2" t="n">
-        <v>92019</v>
+        <v>92020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129374419</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129374400</v>
       </c>
       <c r="B4" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129374458</v>
       </c>
       <c r="B5" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129374446</v>
       </c>
       <c r="B6" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>129380036</v>
       </c>
       <c r="B7" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>129380034</v>
       </c>
       <c r="B8" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129332504</v>
       </c>
       <c r="B2" t="n">
-        <v>92020</v>
+        <v>92025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129374400</v>
       </c>
       <c r="B4" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>129380036</v>
       </c>
       <c r="B7" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>129380034</v>
       </c>
       <c r="B8" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -1230,7 +1230,7 @@
         <v>129380036</v>
       </c>
       <c r="B7" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>129380034</v>
       </c>
       <c r="B8" t="n">
-        <v>90625</v>
+        <v>90629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47774-2025 artfynd.xlsx
+++ b/artfynd/A 47774-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129332504</v>
       </c>
       <c r="B2" t="n">
-        <v>92025</v>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,44 +789,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129374419</v>
+        <v>129374458</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -836,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572731</v>
+        <v>572658</v>
       </c>
       <c r="R3" t="n">
-        <v>6406445</v>
+        <v>6406532</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,39 +899,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129374400</v>
+        <v>129380036</v>
       </c>
       <c r="B4" t="n">
-        <v>92911</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -940,17 +937,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 47774, Lörstad, Sm</t>
+          <t>A47774 Lörstad, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572739</v>
+        <v>572732</v>
       </c>
       <c r="R4" t="n">
-        <v>6406392</v>
+        <v>6406447</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,22 +992,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129374458</v>
+        <v>129380034</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,45 +1015,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 47774, Lörstad, Sm</t>
+          <t>A47774 Lörstad, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572658</v>
+        <v>572732</v>
       </c>
       <c r="R5" t="n">
-        <v>6406532</v>
+        <v>6406447</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,39 +1084,35 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129374446</v>
+        <v>129374400</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>93233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,31 +1120,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572696</v>
+        <v>572739</v>
       </c>
       <c r="R6" t="n">
-        <v>6406574</v>
+        <v>6406392</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,17 +1193,13 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1227,55 +1218,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129380036</v>
+        <v>129374446</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A47774 Lörstad, Sm</t>
+          <t>A 47774, Lörstad, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572732</v>
+        <v>572696</v>
       </c>
       <c r="R7" t="n">
-        <v>6406447</v>
+        <v>6406574</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,35 +1299,39 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129380034</v>
+        <v>129374419</v>
       </c>
       <c r="B8" t="n">
-        <v>90629</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,44 +1339,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A47774 Lörstad, Sm</t>
+          <t>A 47774, Lörstad, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572732</v>
+        <v>572731</v>
       </c>
       <c r="R8" t="n">
-        <v>6406447</v>
+        <v>6406445</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,19 +1419,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
